--- a/stories/arbres/ATOM-EMO.LEX.005-06.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Élodie arrose les fleurs avec papa. L'eau est fraîche. Inès prend l'arrosoir. L'eau part. Élodie sent son visage chaud. Son ventre est dur. Élodie dit : je suis en colère. Elle ouvre les doigts. Les mains restent loin. Élodie peut s'éloigner. Elle s'éloigne vers le banc. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte. Élodie dit : papa, je suis en colère. L'arrosoir est parti. Papa écoute. Plus tard, au salon, elles font un puzzle. Une pièce glisse. Inès la prend. Élodie sent encore la chaleur. Elle se souvient. Elle dit : je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Papa dit : tu as nommé. Tu as repris le geste. Même leçon, autre lieu. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+          <t>Élodie arrose les fleurs avec papa. L'eau est fraîche. Inès prend l'arrosoir. L'eau part. Élodie sent son visage chaud. Son ventre est dur. Je suis en colère. Elle ouvre les doigts. Les mains restent loin. Élodie peut s'éloigner. Elle s'éloigne vers le banc. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte. Papa, je suis en colère. L'arrosoir est parti. Papa écoute. Plus tard, au salon, elles font un puzzle. Une pièce glisse. Inès la prend. Élodie sent encore la chaleur. Elle se souvient. Je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Tu as nommé. Tu as repris le geste. Même leçon, autre lieu. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Élodie arrose les fleurs avec papa. L'eau est fraîche. Inès prend l'arrosoir. L'eau part. Élodie sent son visage chaud. Son ventre est dur.
+enfant-f|Je suis en colère. Elle ouvre les doigts.
+narrateur|Les mains restent loin. Élodie peut s'éloigner. Elle s'éloigne vers le banc. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte.
+enfant-f|Papa, je suis en colère. L'arrosoir est parti. Papa écoute. Plus tard, au salon, elles font un puzzle.
+narrateur|Une pièce glisse. Inès la prend. Élodie sent encore la chaleur. Elle se souvient.
+narrateur|Je suis en colère.
+narrateur|Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle.
+papa|Tu as nommé. Tu as repris le geste. Même leçon, autre lieu.
+narrateur|La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1498,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|L'arrosoir d'Élodie part. Que fait-elle de sa colère ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Élodie a nommé sa colère. Mains loin. Elle peut s'éloigner. Elle va vers papa, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1834,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Élodie s'assoit près de papa. Le puzzle reste sur la table.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2001,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-06.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,7 @@
 narrateur|La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1505,6 +1511,7 @@
           <t>narrateur|L'arrosoir d'Élodie part. Que fait-elle de sa colère ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1683,7 @@
           <t>narrateur|Élodie a nommé sa colère. Mains loin. Elle peut s'éloigner. Elle va vers papa, l'adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Élodie s'assoit près de papa. Le puzzle reste sur la table.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.005-06.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Élodie nomme sa colère deux fois</t>
+          <t>L'arrosoir de Victorina</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,7 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +831,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorina arrose la menthe. Sarah prend l'arrosoir. Elle nomme sa colère, s'éloigne, rejoint papa. Au salon, une pièce de puzzle glisse. Elle reprend le geste.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1185,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Élodie arrose les fleurs avec papa. L'eau est fraîche. Inès prend l'arrosoir. L'eau part. Élodie sent son visage chaud. Son ventre est dur. Je suis en colère. Elle ouvre les doigts. Les mains restent loin. Élodie peut s'éloigner. Elle s'éloigne vers le banc. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte. Papa, je suis en colère. L'arrosoir est parti. Papa écoute. Plus tard, au salon, elles font un puzzle. Une pièce glisse. Inès la prend. Élodie sent encore la chaleur. Elle se souvient. Je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Tu as nommé. Tu as repris le geste. Même leçon, autre lieu. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+          <t>Une goutte tombe du bec de zinc. Elle éclate sur le gravier. Le gravier fait un petit bruit clair. La menthe sent fort, tout près. Les feuilles sont fraîches et un peu poilues. Une coccinelle marche sur une tige. Des sandales mouillées attendent près de la porte. Victorina, tu as vu la coccinelle ? Oui, papa. Elle a des points noirs. L'eau est fraîche, ce matin. En ce moment, Victorina arrose les fleurs. L'eau est fraîche sur ses doigts. Sarah est là, près des plants. La menthe a soif. Tout doux, un peu d'eau. Sarah prend l'arrosoir. L'eau part sur le gravier. Victorina sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Elle ouvre les doigts. Les mains restent loin de Sarah. Victorina peut s'éloigner. Elle s'éloigne vers le banc. Le bois du banc est tiède. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte près de la porte. Papa, je suis en colère. L'arrosoir est parti. Tu as dit le nom. Tu es en colère. Bravo, Victorina. Tes mains sont restées loin. Tu t'es éloignée. Tu es venue vers moi. Tu as fait du bon travail. Tu veux t'asseoir un peu ? Oui, papa. Victorina pose sa main dans la main de papa. La menthe sent encore. Plus tard, au salon, elles font un puzzle. Le tapis est doux sous les genoux. Une pièce glisse. Sarah la prend. Victorina sent encore la chaleur. Elle se souvient. Je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Papa, je suis en colère encore. Tu as nommé. Tu as repris le geste. Même leçon, autre lieu. Bravo. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1325,77 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Élodie arrose les fleurs avec papa. L'eau est fraîche. Inès prend l'arrosoir. L'eau part. Élodie sent son visage chaud. Son ventre est dur.
-enfant-f|Je suis en colère. Elle ouvre les doigts.
-narrateur|Les mains restent loin. Élodie peut s'éloigner. Elle s'éloigne vers le banc. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte.
-enfant-f|Papa, je suis en colère. L'arrosoir est parti. Papa écoute. Plus tard, au salon, elles font un puzzle.
-narrateur|Une pièce glisse. Inès la prend. Élodie sent encore la chaleur. Elle se souvient.
-narrateur|Je suis en colère.
-narrateur|Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle.
-papa|Tu as nommé. Tu as repris le geste. Même leçon, autre lieu.
-narrateur|La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une goutte tombe du bec de zinc.
+narrateur|Elle éclate sur le gravier.
+narrateur|Le gravier fait un petit bruit clair.
+narrateur|La menthe sent fort, tout près.
+narrateur|Les feuilles sont fraîches et un peu poilues.
+narrateur|Une coccinelle marche sur une tige.
+narrateur|Des sandales mouillées attendent près de la porte.
+papa|Victorina, tu as vu la coccinelle ?
+enfant-f|Oui, papa.
+enfant-f|Elle a des points noirs.
+papa|L'eau est fraîche, ce matin.
+narrateur|En ce moment, Victorina arrose les fleurs.
+narrateur|L'eau est fraîche sur ses doigts.
+narrateur|Sarah est là, près des plants.
+enfant-f|La menthe a soif.
+papa|Tout doux, un peu d'eau.
+narrateur|Sarah prend l'arrosoir.
+narrateur|L'eau part sur le gravier.
+narrateur|Victorina sent son visage chaud.
+narrateur|Son ventre est dur.
+narrateur|Être en colère, ce n'est pas honteux.
+enfant-f|Je suis en colère.
+narrateur|Elle ouvre les doigts.
+narrateur|Les mains restent loin de Sarah.
+narrateur|Victorina peut s'éloigner.
+narrateur|Elle s'éloigne vers le banc.
+narrateur|Le bois du banc est tiède.
+narrateur|Elle souffle trois fois.
+narrateur|Puis elle va vers papa.
+narrateur|Papa est l'adulte près de la porte.
+enfant-f|Papa, je suis en colère.
+enfant-f|L'arrosoir est parti.
+papa|Tu as dit le nom.
+papa|Tu es en colère.
+papa|Bravo, Victorina.
+papa|Tes mains sont restées loin.
+papa|Tu t'es éloignée.
+papa|Tu es venue vers moi.
+papa|Tu as fait du bon travail.
+papa|Tu veux t'asseoir un peu ?
+enfant-f|Oui, papa.
+narrateur|Victorina pose sa main dans la main de papa.
+narrateur|La menthe sent encore.
+narrateur|Plus tard, au salon, elles font un puzzle.
+narrateur|Le tapis est doux sous les genoux.
+narrateur|Une pièce glisse.
+narrateur|Sarah la prend.
+narrateur|Victorina sent encore la chaleur.
+narrateur|Elle se souvient.
+enfant-f|Je suis en colère.
+narrateur|Les mains restent loin.
+narrateur|Elle peut s'éloigner.
+narrateur|Elle s'éloigne.
+narrateur|Elle va vers papa, l'adulte.
+narrateur|Elle souffle.
+enfant-f|Papa, je suis en colère encore.
+papa|Tu as nommé.
+papa|Tu as repris le geste.
+papa|Même leçon, autre lieu.
+papa|Bravo.
+narrateur|La colère a un nom.
+narrateur|Les mains restent loin.
+narrateur|On s'éloigne.
+narrateur|On va vers un adulte.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>jardin</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1348,7 +1420,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>L'arrosoir d'Élodie part. Que fait-elle de sa colère ?</t>
+          <t>L'arrosoir de Victorina part. Que fait-elle de sa colère ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,7 +1580,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|L'arrosoir d'Élodie part. Que fait-elle de sa colère ?</t>
+          <t>narrateur|L'arrosoir de Victorina part.
+narrateur|Que fait-elle de sa colère ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1536,7 +1609,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Élodie a nommé sa colère. Mains loin. Elle peut s'éloigner. Elle va vers papa, l'adulte.</t>
+          <t>Victorina a nommé sa colère. Mains loin. Elle peut s'éloigner. Elle va vers papa, l'adulte. Tu as dit : je suis en colère. Au jardin, puis au salon. Bravo, Victorina. J'ai ouvert les doigts. Oui. Et tu es venue vers moi. L'arrosoir repose près de la porte. Le zinc est encore un peu mouillé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1680,7 +1753,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Élodie a nommé sa colère. Mains loin. Elle peut s'éloigner. Elle va vers papa, l'adulte.</t>
+          <t>narrateur|Victorina a nommé sa colère.
+narrateur|Mains loin.
+narrateur|Elle peut s'éloigner.
+narrateur|Elle va vers papa, l'adulte.
+papa|Tu as dit : je suis en colère.
+papa|Au jardin, puis au salon.
+papa|Bravo, Victorina.
+enfant-f|J'ai ouvert les doigts.
+papa|Oui.
+papa|Et tu es venue vers moi.
+narrateur|L'arrosoir repose près de la porte.
+narrateur|Le zinc est encore un peu mouillé.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1708,7 +1792,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Élodie s'assoit près de papa. Le puzzle reste sur la table.</t>
+          <t>Victorina s'assoit près de papa. Le puzzle reste sur la table. On laisse les pièces pour plus tard ? Oui, papa. Les sandales sèchent près de la porte. Tu as nommé deux fois. C'est du bon travail. La menthe sent encore, un peu. On ira la voir demain. Tout doux, un peu d'eau. La coccinelle n'est plus sur la tige. Le banc du jardin reste tiède.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,10 +1928,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Élodie s'assoit près de papa. Le puzzle reste sur la table.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Victorina s'assoit près de papa.
+narrateur|Le puzzle reste sur la table.
+papa|On laisse les pièces pour plus tard ?
+enfant-f|Oui, papa.
+narrateur|Les sandales sèchent près de la porte.
+papa|Tu as nommé deux fois.
+papa|C'est du bon travail.
+enfant-f|La menthe sent encore, un peu.
+papa|On ira la voir demain.
+enfant-f|Tout doux, un peu d'eau.
+narrateur|La coccinelle n'est plus sur la tige.
+narrateur|Le banc du jardin reste tiède.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>jardin</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,7 +1971,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit : je suis en colère. Je me suis éloignée. Je suis allée vers papa. Bravo, Victorina. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,7 +2111,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'ai dit : je suis en colère.
+enfant-f|Je me suis éloignée.
+enfant-f|Je suis allée vers papa.
+papa|Bravo, Victorina.
+papa|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2034,7 +2138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2176,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-06.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-06.xlsx
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une goutte tombe du bec de zinc. Elle éclate sur le gravier. Le gravier fait un petit bruit clair. La menthe sent fort, tout près. Les feuilles sont fraîches et un peu poilues. Une coccinelle marche sur une tige. Des sandales mouillées attendent près de la porte. Victorina, tu as vu la coccinelle ? Oui, papa. Elle a des points noirs. L'eau est fraîche, ce matin. En ce moment, Victorina arrose les fleurs. L'eau est fraîche sur ses doigts. Sarah est là, près des plants. La menthe a soif. Tout doux, un peu d'eau. Sarah prend l'arrosoir. L'eau part sur le gravier. Victorina sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Elle ouvre les doigts. Les mains restent loin de Sarah. Victorina peut s'éloigner. Elle s'éloigne vers le banc. Le bois du banc est tiède. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte près de la porte. Papa, je suis en colère. L'arrosoir est parti. Tu as dit le nom. Tu es en colère. Bravo, Victorina. Tes mains sont restées loin. Tu t'es éloignée. Tu es venue vers moi. Tu as fait du bon travail. Tu veux t'asseoir un peu ? Oui, papa. Victorina pose sa main dans la main de papa. La menthe sent encore. Plus tard, au salon, elles font un puzzle. Le tapis est doux sous les genoux. Une pièce glisse. Sarah la prend. Victorina sent encore la chaleur. Elle se souvient. Je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Papa, je suis en colère encore. Tu as nommé. Tu as repris le geste. Même leçon, autre lieu. Bravo. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+          <t>Une goutte tombe du bec de zinc. Elle éclate sur le gravier. Le gravier fait un petit bruit clair. La menthe sent fort, tout près. Les feuilles sont fraîches et un peu poilues. Une coccinelle marche sur une tige. Des sandales mouillées attendent près de la porte. Victorina, tu as vu la coccinelle ? Oui, papa. Elle a des points noirs. L'eau est fraîche, ce matin. En ce moment, Victorina arrose les fleurs. L'eau est fraîche sur ses doigts. Sarah est là, près des plants. La menthe a soif. Tout doux, un peu d'eau. Sarah prend l'arrosoir. L'eau part sur le gravier. Victorina sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Elle ouvre les doigts. Les mains restent loin de Sarah. Victorina peut s'éloigner. Elle s'éloigne vers le banc. Le bois du banc est tiède. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte près de la porte. Papa, je suis en colère. L'arrosoir est parti. Tu as dit le nom. Tu es en colère. Bravo, Victorina. Tes mains sont restées loin. Tu t'es éloignée. Tu es venue vers moi. Tu veux t'asseoir un peu ? Oui, papa. Victorina pose sa main dans la main de papa. La menthe sent encore. Plus tard, au salon, elles font un puzzle. Le tapis est doux sous les genoux. Une pièce glisse. Sarah la prend. Victorina sent encore la chaleur. Elle se souvient. Je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Papa, je suis en colère encore. Tu as nommé. Tu as repris le geste. Même leçon, autre lieu. Bravo. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Élodie arrose les fleurs avec papa. L'eau est fraîche. Inès prend l'arrosoir. L'eau part. Élodie sent son visage chaud. Son ventre est dur. Élodie dit : je suis en &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt;. Elle ouvre les doigts. Les mains restent loin. Élodie peut s'éloigner. Elle s'éloigne vers le banc. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte. Élodie dit : papa, je suis en colère. L'arrosoir est parti. Papa écoute. Plus tard, au salon, elles font un puzzle. Une pièce glisse. Inès la prend. Élodie sent encore la chaleur. Elle se souvient. Elle dit : je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Papa dit : tu as nommé. Tu as repris le geste. Même leçon, autre lieu. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une goutte tombe du bec de zinc. Elle éclate sur le gravier. Le gravier fait un petit bruit clair. La menthe sent fort, tout près. Les feuilles sont fraîches et un peu poilues. Une coccinelle marche sur une tige. Des sandales mouillées attendent près de la porte. Victorina, tu as vu la coccinelle ? Oui, papa. Elle a des points noirs. L'eau est fraîche, ce matin. En ce moment, Victorina arrose les fleurs. L'eau est fraîche sur ses doigts. Sarah est là, près des plants. La menthe a soif. Tout doux, un peu d'eau. Sarah prend l'arrosoir. L'eau part sur le gravier. Victorina sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Elle ouvre les doigts. Les mains restent loin de Sarah. Victorina peut s'éloigner. Elle s'éloigne vers le banc. Le bois du banc est tiède. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte près de la porte. Papa, je suis en colère. L'arrosoir est parti. Tu as dit le nom. Tu es en colère. Bravo, Victorina. Tes mains sont restées loin. Tu t'es éloignée. Tu es venue vers moi. Tu veux t'asseoir un peu ? Oui, papa. Victorina pose sa main dans la main de papa. La menthe sent encore. Plus tard, au salon, elles font un puzzle. Le tapis est doux sous les genoux. Une pièce glisse. Sarah la prend. Victorina sent encore la chaleur. Elle se souvient. Je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Papa, je suis en colère encore. Tu as nommé. Tu as repris le geste. Même leçon, autre lieu. Bravo. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1363,7 +1363,6 @@
 papa|Tes mains sont restées loin.
 papa|Tu t'es éloignée.
 papa|Tu es venue vers moi.
-papa|Tu as fait du bon travail.
 papa|Tu veux t'asseoir un peu ?
 enfant-f|Oui, papa.
 narrateur|Victorina pose sa main dans la main de papa.
@@ -1425,7 +1424,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;L'arrosoir d'Élodie part. Que fait-elle de sa &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt; ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'arrosoir de Victorina part. Que fait-elle de sa colère ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1584,7 +1583,6 @@
 narrateur|Que fait-elle de sa colère ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1614,7 +1612,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Élodie a nommé sa &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt;. Mains loin. Elle peut s'éloigner. Elle va vers papa, l'adulte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina a nommé sa colère. Mains loin. Elle peut s'éloigner. Elle va vers papa, l'adulte. Tu as dit : je suis en colère. Au jardin, puis au salon. Bravo, Victorina. J'ai ouvert les doigts. Oui. Et tu es venue vers moi. L'arrosoir repose près de la porte. Le zinc est encore un peu mouillé.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1767,7 +1765,6 @@
 narrateur|Le zinc est encore un peu mouillé.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1792,12 +1789,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Victorina s'assoit près de papa. Le puzzle reste sur la table. On laisse les pièces pour plus tard ? Oui, papa. Les sandales sèchent près de la porte. Tu as nommé deux fois. C'est du bon travail. La menthe sent encore, un peu. On ira la voir demain. Tout doux, un peu d'eau. La coccinelle n'est plus sur la tige. Le banc du jardin reste tiède.</t>
+          <t>Victorina s'assoit près de papa. Le puzzle reste sur la table. On laisse les pièces pour plus tard ? Oui, papa. Les sandales sèchent près de la porte. Tu as nommé deux fois. La menthe sent encore, un peu. On ira la voir demain. Tout doux, un peu d'eau. La coccinelle n'est plus sur la tige. Le banc du jardin reste tiède.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Élodie s'assoit près de papa. Le puzzle reste sur la table.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorina s'assoit près de papa. Le puzzle reste sur la table. On laisse les pièces pour plus tard ? Oui, papa. Les sandales sèchent près de la porte. Tu as nommé deux fois. La menthe sent encore, un peu. On ira la voir demain. Tout doux, un peu d'eau. La coccinelle n'est plus sur la tige. Le banc du jardin reste tiède.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1934,7 +1931,6 @@
 enfant-f|Oui, papa.
 narrateur|Les sandales sèchent près de la porte.
 papa|Tu as nommé deux fois.
-papa|C'est du bon travail.
 enfant-f|La menthe sent encore, un peu.
 papa|On ira la voir demain.
 enfant-f|Tout doux, un peu d'eau.
@@ -1971,12 +1967,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit : je suis en colère. Je me suis éloignée. Je suis allée vers papa. Bravo, Victorina. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>J'ai dit : je suis en colère. Je me suis éloignée. Je suis allée vers papa. Bravo, Victorina.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit : je suis en colère. Je me suis éloignée. Je suis allée vers papa. Bravo, Victorina.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2114,12 +2110,9 @@
           <t>enfant-f|J'ai dit : je suis en colère.
 enfant-f|Je me suis éloignée.
 enfant-f|Je suis allée vers papa.
-papa|Bravo, Victorina.
-papa|Tu as fait du bon travail.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|Bravo, Victorina.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2138,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2183,6 +2176,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-06.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-06.xlsx
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -684,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Élodie, Inès, papa</t>
+          <t>Victorina, Sarah, papa</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-06.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-06.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Victorina arrose la menthe. Sarah prend l'arrosoir. Elle nomme sa colère, s'éloigne, rejoint papa. Au salon, une pièce de puzzle glisse. Elle reprend le geste.</t>
+          <t>Victorina veut arroser la menthe. Sarah prend l'arrosoir. Elle dit sa colère, va au banc, rejoint papa. Au salon, une pièce glisse. Elle recule encore. La menthe boit, le soir.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Une goutte tombe du bec de zinc. Elle éclate sur le gravier. Le gravier fait un petit bruit clair. La menthe sent fort, tout près. Les feuilles sont fraîches et un peu poilues. Une coccinelle marche sur une tige. Des sandales mouillées attendent près de la porte. Victorina, tu as vu la coccinelle ? Oui, papa. Elle a des points noirs. L'eau est fraîche, ce matin. En ce moment, Victorina arrose les fleurs. L'eau est fraîche sur ses doigts. Sarah est là, près des plants. La menthe a soif. Tout doux, un peu d'eau. Sarah prend l'arrosoir. L'eau part sur le gravier. Victorina sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Elle ouvre les doigts. Les mains restent loin de Sarah. Victorina peut s'éloigner. Elle s'éloigne vers le banc. Le bois du banc est tiède. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte près de la porte. Papa, je suis en colère. L'arrosoir est parti. Tu as dit le nom. Tu es en colère. Bravo, Victorina. Tes mains sont restées loin. Tu t'es éloignée. Tu es venue vers moi. Tu veux t'asseoir un peu ? Oui, papa. Victorina pose sa main dans la main de papa. La menthe sent encore. Plus tard, au salon, elles font un puzzle. Le tapis est doux sous les genoux. Une pièce glisse. Sarah la prend. Victorina sent encore la chaleur. Elle se souvient. Je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Papa, je suis en colère encore. Tu as nommé. Tu as repris le geste. Même leçon, autre lieu. Bravo. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+          <t>Une goutte tombe du bec de zinc. Elle éclate sur le gravier. Le gravier fait un petit bruit clair. La menthe sent fort, tout près. Les feuilles sont fraîches et un peu poilues. Une coccinelle marche sur une tige. Des sandales mouillées attendent près de la porte. Victorina, tu as vu la coccinelle ? Oui, papa. Elle a des points noirs. L'eau est fraîche, ce matin. Je veux arroser la menthe. Tout doux, un peu d'eau. En ce moment, Victorina arrose les fleurs. L'eau est fraîche sur ses doigts. Sarah est là, près des plants. La menthe a soif. Le bec de zinc goutte encore. Sarah prend l'arrosoir. L'eau part sur le gravier. Victorina sent son visage chaud. Son ventre est dur. Je suis en colère. Elle ouvre les doigts. Les mains restent loin de Sarah. Elle recule vers le banc. Le bois du banc est tiède. Elle souffle trois fois. Puis elle va vers papa. Papa, l'arrosoir est parti. Je t'écoute. Tu veux t'asseoir un peu ? Oui, papa. Victorina pose sa main dans la main de papa. La menthe sent encore. Plus tard, au salon, le tapis est doux. Un puzzle attend près de la table basse. Une pièce bleue brille un peu. Je veux le ciel, là. Elle est lisse, cette pièce. La pièce glisse. Sarah la prend. Le visage de Victorina redevient chaud. Son ventre se durcit. Elle ouvre encore les doigts. Elle recule vers la fenêtre. Le bois du rebord est froid. Elle va près de papa. Sarah a pris la pièce. Je t'écoute. On reste près de la fenêtre ? Un moment. Victorina souffle. Le ventre se desserre un peu. La menthe t'attend dehors, tu crois ? Oui. Elle a encore soif.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Une goutte tombe du bec de zinc. Elle éclate sur le gravier. Le gravier fait un petit bruit clair. La menthe sent fort, tout près. Les feuilles sont fraîches et un peu poilues. Une coccinelle marche sur une tige. Des sandales mouillées attendent près de la porte. Victorina, tu as vu la coccinelle ? Oui, papa. Elle a des points noirs. L'eau est fraîche, ce matin. En ce moment, Victorina arrose les fleurs. L'eau est fraîche sur ses doigts. Sarah est là, près des plants. La menthe a soif. Tout doux, un peu d'eau. Sarah prend l'arrosoir. L'eau part sur le gravier. Victorina sent son visage chaud. Son ventre est dur. Être en colère, ce n'est pas honteux. Je suis en colère. Elle ouvre les doigts. Les mains restent loin de Sarah. Victorina peut s'éloigner. Elle s'éloigne vers le banc. Le bois du banc est tiède. Elle souffle trois fois. Puis elle va vers papa. Papa est l'adulte près de la porte. Papa, je suis en colère. L'arrosoir est parti. Tu as dit le nom. Tu es en colère. Bravo, Victorina. Tes mains sont restées loin. Tu t'es éloignée. Tu es venue vers moi. Tu veux t'asseoir un peu ? Oui, papa. Victorina pose sa main dans la main de papa. La menthe sent encore. Plus tard, au salon, elles font un puzzle. Le tapis est doux sous les genoux. Une pièce glisse. Sarah la prend. Victorina sent encore la chaleur. Elle se souvient. Je suis en colère. Les mains restent loin. Elle peut s'éloigner. Elle s'éloigne. Elle va vers papa, l'adulte. Elle souffle. Papa, je suis en colère encore. Tu as nommé. Tu as repris le geste. Même leçon, autre lieu. Bravo. La colère a un nom. Les mains restent loin. On s'éloigne. On va vers un adulte.</t>
+          <t>Une goutte tombe du bec de zinc. Elle éclate sur le gravier. Le gravier fait un petit bruit clair. La menthe sent fort, tout près. Les feuilles sont fraîches et un peu poilues. Une coccinelle marche sur une tige. Des sandales mouillées attendent près de la porte. Victorina, tu as vu la coccinelle ? Oui, papa. Elle a des points noirs. L'eau est fraîche, ce matin. Je veux arroser la menthe. Tout doux, un peu d'eau. En ce moment, Victorina arrose les fleurs. L'eau est fraîche sur ses doigts. Sarah est là, près des plants. La menthe a soif. Le bec de zinc goutte encore. Sarah prend l'arrosoir. L'eau part sur le gravier. Victorina sent son visage chaud. Son ventre est dur. Je suis en colère. Elle ouvre les doigts. Les mains restent loin de Sarah. Elle recule vers le banc. Le bois du banc est tiède. Elle souffle trois fois. Puis elle va vers papa. Papa, l'arrosoir est parti. Je t'écoute. Tu veux t'asseoir un peu ? Oui, papa. Victorina pose sa main dans la main de papa. La menthe sent encore. Plus tard, au salon, le tapis est doux. Un puzzle attend près de la table basse. Une pièce bleue brille un peu. Je veux le ciel, là. Elle est lisse, cette pièce. La pièce glisse. Sarah la prend. Le visage de Victorina redevient chaud. Son ventre se durcit. Elle ouvre encore les doigts. Elle recule vers la fenêtre. Le bois du rebord est froid. Elle va près de papa. Sarah a pris la pièce. Je t'écoute. On reste près de la fenêtre ? Un moment. Victorina souffle. Le ventre se desserre un peu. La menthe t'attend dehors, tu crois ? Oui. Elle a encore soif.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1335,58 +1335,52 @@
 enfant-f|Oui, papa.
 enfant-f|Elle a des points noirs.
 papa|L'eau est fraîche, ce matin.
+enfant-f|Je veux arroser la menthe.
+papa|Tout doux, un peu d'eau.
 narrateur|En ce moment, Victorina arrose les fleurs.
 narrateur|L'eau est fraîche sur ses doigts.
 narrateur|Sarah est là, près des plants.
 enfant-f|La menthe a soif.
-papa|Tout doux, un peu d'eau.
+papa|Le bec de zinc goutte encore.
 narrateur|Sarah prend l'arrosoir.
 narrateur|L'eau part sur le gravier.
 narrateur|Victorina sent son visage chaud.
 narrateur|Son ventre est dur.
-narrateur|Être en colère, ce n'est pas honteux.
 enfant-f|Je suis en colère.
 narrateur|Elle ouvre les doigts.
 narrateur|Les mains restent loin de Sarah.
-narrateur|Victorina peut s'éloigner.
-narrateur|Elle s'éloigne vers le banc.
+narrateur|Elle recule vers le banc.
 narrateur|Le bois du banc est tiède.
 narrateur|Elle souffle trois fois.
 narrateur|Puis elle va vers papa.
-narrateur|Papa est l'adulte près de la porte.
-enfant-f|Papa, je suis en colère.
-enfant-f|L'arrosoir est parti.
-papa|Tu as dit le nom.
-papa|Tu es en colère.
-papa|Bravo, Victorina.
-papa|Tes mains sont restées loin.
-papa|Tu t'es éloignée.
-papa|Tu es venue vers moi.
+enfant-f|Papa, l'arrosoir est parti.
+papa|Je t'écoute.
 papa|Tu veux t'asseoir un peu ?
 enfant-f|Oui, papa.
 narrateur|Victorina pose sa main dans la main de papa.
 narrateur|La menthe sent encore.
-narrateur|Plus tard, au salon, elles font un puzzle.
-narrateur|Le tapis est doux sous les genoux.
-narrateur|Une pièce glisse.
+narrateur|Plus tard, au salon, le tapis est doux.
+narrateur|Un puzzle attend près de la table basse.
+narrateur|Une pièce bleue brille un peu.
+enfant-f|Je veux le ciel, là.
+papa|Elle est lisse, cette pièce.
+narrateur|La pièce glisse.
 narrateur|Sarah la prend.
-narrateur|Victorina sent encore la chaleur.
-narrateur|Elle se souvient.
-enfant-f|Je suis en colère.
-narrateur|Les mains restent loin.
-narrateur|Elle peut s'éloigner.
-narrateur|Elle s'éloigne.
-narrateur|Elle va vers papa, l'adulte.
-narrateur|Elle souffle.
-enfant-f|Papa, je suis en colère encore.
-papa|Tu as nommé.
-papa|Tu as repris le geste.
-papa|Même leçon, autre lieu.
-papa|Bravo.
-narrateur|La colère a un nom.
-narrateur|Les mains restent loin.
-narrateur|On s'éloigne.
-narrateur|On va vers un adulte.</t>
+narrateur|Le visage de Victorina redevient chaud.
+narrateur|Son ventre se durcit.
+narrateur|Elle ouvre encore les doigts.
+narrateur|Elle recule vers la fenêtre.
+narrateur|Le bois du rebord est froid.
+narrateur|Elle va près de papa.
+enfant-f|Sarah a pris la pièce.
+papa|Je t'écoute.
+papa|On reste près de la fenêtre ?
+enfant-f|Un moment.
+narrateur|Victorina souffle.
+narrateur|Le ventre se desserre un peu.
+papa|La menthe t'attend dehors, tu crois ?
+enfant-f|Oui.
+enfant-f|Elle a encore soif.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1418,12 +1412,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>L'arrosoir de Victorina part. Que fait-elle de sa colère ?</t>
+          <t>L'arrosoir de Victorina part. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>L'arrosoir de Victorina part. Que fait-elle de sa colère ?</t>
+          <t>L'arrosoir de Victorina part. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1453,7 +1447,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Élodie nomme sa colère. Puis elle va où ?</t>
+          <t>Victorina ouvre les doigts. Puis elle va où ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1495,14 +1489,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1579,7 +1573,7 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|L'arrosoir de Victorina part.
-narrateur|Que fait-elle de sa colère ?</t>
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1606,12 +1600,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a nommé sa colère. Mains loin. Elle peut s'éloigner. Elle va vers papa, l'adulte. Tu as dit : je suis en colère. Au jardin, puis au salon. Bravo, Victorina. J'ai ouvert les doigts. Oui. Et tu es venue vers moi. L'arrosoir repose près de la porte. Le zinc est encore un peu mouillé.</t>
+          <t>Victorina revient près de la porte. L'arrosoir repose contre le zinc. On va voir la menthe ? Oui. Tout doux. Sarah tend l'anse. Victorina verse un filet d'eau. La terre devient sombre. Bravo, Victorina. Elle boit. Oui. Les sandales sèchent près de la porte. Le zinc est encore un peu mouillé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Victorina a nommé sa colère. Mains loin. Elle peut s'éloigner. Elle va vers papa, l'adulte. Tu as dit : je suis en colère. Au jardin, puis au salon. Bravo, Victorina. J'ai ouvert les doigts. Oui. Et tu es venue vers moi. L'arrosoir repose près de la porte. Le zinc est encore un peu mouillé.</t>
+          <t>Victorina revient près de la porte. L'arrosoir repose contre le zinc. On va voir la menthe ? Oui. Tout doux. Sarah tend l'anse. Victorina verse un filet d'eau. La terre devient sombre. Bravo, Victorina. Elle boit. Oui. Les sandales sèchent près de la porte. Le zinc est encore un peu mouillé.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1674,7 +1668,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1750,17 +1744,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Victorina a nommé sa colère.
-narrateur|Mains loin.
-narrateur|Elle peut s'éloigner.
-narrateur|Elle va vers papa, l'adulte.
-papa|Tu as dit : je suis en colère.
-papa|Au jardin, puis au salon.
+          <t>narrateur|Victorina revient près de la porte.
+narrateur|L'arrosoir repose contre le zinc.
+papa|On va voir la menthe ?
+enfant-f|Oui.
+enfant-f|Tout doux.
+narrateur|Sarah tend l'anse.
+narrateur|Victorina verse un filet d'eau.
+narrateur|La terre devient sombre.
 papa|Bravo, Victorina.
-enfant-f|J'ai ouvert les doigts.
+enfant-f|Elle boit.
 papa|Oui.
-papa|Et tu es venue vers moi.
-narrateur|L'arrosoir repose près de la porte.
+narrateur|Les sandales sèchent près de la porte.
 narrateur|Le zinc est encore un peu mouillé.</t>
         </is>
       </c>
@@ -1788,12 +1783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Victorina s'assoit près de papa. Le puzzle reste sur la table. On laisse les pièces pour plus tard ? Oui, papa. Les sandales sèchent près de la porte. Tu as nommé deux fois. La menthe sent encore, un peu. On ira la voir demain. Tout doux, un peu d'eau. La coccinelle n'est plus sur la tige. Le banc du jardin reste tiède.</t>
+          <t>Victorina s'assoit près de papa. Le puzzle reste sur la table. On laisse les pièces pour plus tard ? Oui, papa. Une feuille de menthe colle à son doigt. Ça sent fort. C'est la menthe. La coccinelle n'est plus sur la tige. Le banc du jardin reste tiède.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Victorina s'assoit près de papa. Le puzzle reste sur la table. On laisse les pièces pour plus tard ? Oui, papa. Les sandales sèchent près de la porte. Tu as nommé deux fois. La menthe sent encore, un peu. On ira la voir demain. Tout doux, un peu d'eau. La coccinelle n'est plus sur la tige. Le banc du jardin reste tiède.</t>
+          <t>Victorina s'assoit près de papa. Le puzzle reste sur la table. On laisse les pièces pour plus tard ? Oui, papa. Une feuille de menthe colle à son doigt. Ça sent fort. C'est la menthe. La coccinelle n'est plus sur la tige. Le banc du jardin reste tiède.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1856,7 +1851,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1928,11 +1923,9 @@
 narrateur|Le puzzle reste sur la table.
 papa|On laisse les pièces pour plus tard ?
 enfant-f|Oui, papa.
-narrateur|Les sandales sèchent près de la porte.
-papa|Tu as nommé deux fois.
-enfant-f|La menthe sent encore, un peu.
-papa|On ira la voir demain.
-enfant-f|Tout doux, un peu d'eau.
+narrateur|Une feuille de menthe colle à son doigt.
+enfant-f|Ça sent fort.
+papa|C'est la menthe.
 narrateur|La coccinelle n'est plus sur la tige.
 narrateur|Le banc du jardin reste tiède.</t>
         </is>
@@ -1966,12 +1959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit : je suis en colère. Je me suis éloignée. Je suis allée vers papa. Bravo, Victorina.</t>
+          <t>La menthe a de l'eau. Merci, Victorina. Une goutte brille encore sur une feuille. Le gravier redevient calme.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit : je suis en colère. Je me suis éloignée. Je suis allée vers papa. Bravo, Victorina.</t>
+          <t>La menthe a de l'eau. Merci, Victorina. Une goutte brille encore sur une feuille. Le gravier redevient calme.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2034,7 +2027,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2106,10 +2099,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-f|J'ai dit : je suis en colère.
-enfant-f|Je me suis éloignée.
-enfant-f|Je suis allée vers papa.
-papa|Bravo, Victorina.</t>
+          <t>enfant-f|La menthe a de l'eau.
+papa|Merci, Victorina.
+narrateur|Une goutte brille encore sur une feuille.
+narrateur|Le gravier redevient calme.</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2180,6 +2173,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
